--- a/dataset_t6_grouped/results2/G5/G5_T6758_W0045F0003T0006Z000C1N78_analysis.xlsx
+++ b/dataset_t6_grouped/results2/G5/G5_T6758_W0045F0003T0006Z000C1N78_analysis.xlsx
@@ -480,16 +480,16 @@
         <v>1</v>
       </c>
       <c r="C2" t="n">
-        <v>4.104286279292892</v>
+        <v>0.6669465203850949</v>
       </c>
       <c r="D2" t="n">
-        <v>7.90653350379924</v>
+        <v>1.284811694367377</v>
       </c>
       <c r="E2" t="n">
-        <v>12.78042031339302</v>
+        <v>2.076818300926367</v>
       </c>
       <c r="F2" t="n">
-        <v>11.58792849519896</v>
+        <v>1.883038380469831</v>
       </c>
       <c r="G2" t="inlineStr">
         <is>
@@ -512,16 +512,16 @@
         <v>2</v>
       </c>
       <c r="C3" t="n">
-        <v>26.0902709321055</v>
+        <v>4.239669026467143</v>
       </c>
       <c r="D3" t="n">
-        <v>8.976690226413183</v>
+        <v>1.458712161792142</v>
       </c>
       <c r="E3" t="n">
-        <v>12.78042031339302</v>
+        <v>2.076818300926367</v>
       </c>
       <c r="F3" t="n">
-        <v>11.58792849519896</v>
+        <v>1.883038380469831</v>
       </c>
       <c r="G3" t="inlineStr">
         <is>
@@ -544,16 +544,16 @@
         <v>3</v>
       </c>
       <c r="C4" t="n">
-        <v>14.35634751079222</v>
+        <v>2.332906470503736</v>
       </c>
       <c r="D4" t="n">
-        <v>9.450027355567068</v>
+        <v>1.535629445279649</v>
       </c>
       <c r="E4" t="n">
-        <v>12.78042031339302</v>
+        <v>2.076818300926367</v>
       </c>
       <c r="F4" t="n">
-        <v>11.58792849519896</v>
+        <v>1.883038380469831</v>
       </c>
       <c r="G4" t="inlineStr">
         <is>
@@ -576,16 +576,16 @@
         <v>4</v>
       </c>
       <c r="C5" t="n">
-        <v>24.10239923892722</v>
+        <v>3.916639876325674</v>
       </c>
       <c r="D5" t="n">
-        <v>19.1049731745428</v>
+        <v>3.104558140863205</v>
       </c>
       <c r="E5" t="n">
-        <v>12.78042031339302</v>
+        <v>2.076818300926367</v>
       </c>
       <c r="F5" t="n">
-        <v>11.58792849519896</v>
+        <v>1.883038380469831</v>
       </c>
       <c r="G5" t="inlineStr">
         <is>
@@ -608,16 +608,16 @@
         <v>5</v>
       </c>
       <c r="C6" t="n">
-        <v>25.1327902907768</v>
+        <v>4.084078422251229</v>
       </c>
       <c r="D6" t="n">
-        <v>25.19293522827783</v>
+        <v>4.093851974595147</v>
       </c>
       <c r="E6" t="n">
-        <v>12.78042031339302</v>
+        <v>2.076818300926367</v>
       </c>
       <c r="F6" t="n">
-        <v>11.58792849519896</v>
+        <v>1.883038380469831</v>
       </c>
       <c r="G6" t="inlineStr">
         <is>
@@ -640,16 +640,16 @@
         <v>6</v>
       </c>
       <c r="C7" t="n">
-        <v>4.891512899702147</v>
+        <v>0.794870846201599</v>
       </c>
       <c r="D7" t="n">
-        <v>32.3967172888357</v>
+        <v>5.2644665594358</v>
       </c>
       <c r="E7" t="n">
-        <v>12.78042031339302</v>
+        <v>2.076818300926367</v>
       </c>
       <c r="F7" t="n">
-        <v>11.58792849519896</v>
+        <v>1.883038380469831</v>
       </c>
       <c r="G7" t="inlineStr">
         <is>
@@ -672,16 +672,16 @@
         <v>7</v>
       </c>
       <c r="C8" t="n">
-        <v>12.67446153919929</v>
+        <v>2.059600000119885</v>
       </c>
       <c r="D8" t="n">
-        <v>13.79311422413372</v>
+        <v>2.24138106142173</v>
       </c>
       <c r="E8" t="n">
-        <v>12.78042031339302</v>
+        <v>2.076818300926367</v>
       </c>
       <c r="F8" t="n">
-        <v>11.58792849519896</v>
+        <v>1.883038380469831</v>
       </c>
       <c r="G8" t="inlineStr">
         <is>
@@ -704,16 +704,16 @@
         <v>8</v>
       </c>
       <c r="C9" t="n">
-        <v>34.89803403076424</v>
+        <v>5.670930529999189</v>
       </c>
       <c r="D9" t="n">
-        <v>37.07732610503442</v>
+        <v>6.025065492068093</v>
       </c>
       <c r="E9" t="n">
-        <v>12.78042031339302</v>
+        <v>2.076818300926367</v>
       </c>
       <c r="F9" t="n">
-        <v>11.58792849519896</v>
+        <v>1.883038380469831</v>
       </c>
       <c r="G9" t="inlineStr">
         <is>
@@ -736,16 +736,16 @@
         <v>9</v>
       </c>
       <c r="C10" t="n">
-        <v>13.88218491725401</v>
+        <v>2.255855049053777</v>
       </c>
       <c r="D10" t="n">
-        <v>48.1936924128591</v>
+        <v>7.831475017089604</v>
       </c>
       <c r="E10" t="n">
-        <v>12.78042031339302</v>
+        <v>2.076818300926367</v>
       </c>
       <c r="F10" t="n">
-        <v>11.58792849519896</v>
+        <v>1.883038380469831</v>
       </c>
       <c r="G10" t="inlineStr">
         <is>
@@ -768,16 +768,16 @@
         <v>10</v>
       </c>
       <c r="C11" t="n">
-        <v>34.78190426353236</v>
+        <v>5.652059442824009</v>
       </c>
       <c r="D11" t="n">
-        <v>21.86394611175196</v>
+        <v>3.552891243159694</v>
       </c>
       <c r="E11" t="n">
-        <v>12.78042031339302</v>
+        <v>2.076818300926367</v>
       </c>
       <c r="F11" t="n">
-        <v>11.58792849519896</v>
+        <v>1.883038380469831</v>
       </c>
       <c r="G11" t="inlineStr">
         <is>
@@ -800,16 +800,16 @@
         <v>11</v>
       </c>
       <c r="C12" t="n">
-        <v>26.47297903356877</v>
+        <v>4.301859092954926</v>
       </c>
       <c r="D12" t="n">
-        <v>25.04736553871781</v>
+        <v>4.070196900041645</v>
       </c>
       <c r="E12" t="n">
-        <v>12.78042031339302</v>
+        <v>2.076818300926367</v>
       </c>
       <c r="F12" t="n">
-        <v>11.58792849519896</v>
+        <v>1.883038380469831</v>
       </c>
       <c r="G12" t="inlineStr">
         <is>
@@ -832,16 +832,16 @@
         <v>12</v>
       </c>
       <c r="C13" t="n">
-        <v>13.73316141574702</v>
+        <v>2.23163873005889</v>
       </c>
       <c r="D13" t="n">
-        <v>12.20351578015381</v>
+        <v>1.983071314274994</v>
       </c>
       <c r="E13" t="n">
-        <v>12.78042031339302</v>
+        <v>2.076818300926367</v>
       </c>
       <c r="F13" t="n">
-        <v>11.58792849519896</v>
+        <v>1.883038380469831</v>
       </c>
       <c r="G13" t="inlineStr">
         <is>
@@ -864,16 +864,16 @@
         <v>13</v>
       </c>
       <c r="C14" t="n">
-        <v>18.87490047406888</v>
+        <v>3.067171327036193</v>
       </c>
       <c r="D14" t="n">
-        <v>28.32174611971953</v>
+        <v>4.602283744454423</v>
       </c>
       <c r="E14" t="n">
-        <v>12.78042031339302</v>
+        <v>2.076818300926367</v>
       </c>
       <c r="F14" t="n">
-        <v>11.58792849519896</v>
+        <v>1.883038380469831</v>
       </c>
       <c r="G14" t="inlineStr">
         <is>
@@ -896,16 +896,16 @@
         <v>14</v>
       </c>
       <c r="C15" t="n">
-        <v>20.59435299069126</v>
+        <v>3.34658236098733</v>
       </c>
       <c r="D15" t="n">
-        <v>13.01795732878723</v>
+        <v>2.115418065927925</v>
       </c>
       <c r="E15" t="n">
-        <v>12.78042031339302</v>
+        <v>2.076818300926367</v>
       </c>
       <c r="F15" t="n">
-        <v>11.58792849519896</v>
+        <v>1.883038380469831</v>
       </c>
       <c r="G15" t="inlineStr">
         <is>
@@ -928,16 +928,16 @@
         <v>15</v>
       </c>
       <c r="C16" t="n">
-        <v>10.92230494059962</v>
+        <v>1.774874552847438</v>
       </c>
       <c r="D16" t="n">
-        <v>26.8607421924161</v>
+        <v>4.364870606267616</v>
       </c>
       <c r="E16" t="n">
-        <v>12.78042031339302</v>
+        <v>2.076818300926367</v>
       </c>
       <c r="F16" t="n">
-        <v>11.58792849519896</v>
+        <v>1.883038380469831</v>
       </c>
       <c r="G16" t="inlineStr">
         <is>
@@ -960,16 +960,16 @@
         <v>16</v>
       </c>
       <c r="C17" t="n">
-        <v>25.69110626559747</v>
+        <v>4.174804768159589</v>
       </c>
       <c r="D17" t="n">
-        <v>20.25591647174267</v>
+        <v>3.291586426658184</v>
       </c>
       <c r="E17" t="n">
-        <v>12.78042031339302</v>
+        <v>2.076818300926367</v>
       </c>
       <c r="F17" t="n">
-        <v>11.58792849519896</v>
+        <v>1.883038380469831</v>
       </c>
       <c r="G17" t="inlineStr">
         <is>
@@ -992,16 +992,16 @@
         <v>17</v>
       </c>
       <c r="C18" t="n">
-        <v>14.03850722228285</v>
+        <v>2.281257423620962</v>
       </c>
       <c r="D18" t="n">
-        <v>28.7276223470962</v>
+        <v>4.668238631403133</v>
       </c>
       <c r="E18" t="n">
-        <v>12.78042031339302</v>
+        <v>2.076818300926367</v>
       </c>
       <c r="F18" t="n">
-        <v>11.58792849519896</v>
+        <v>1.883038380469831</v>
       </c>
       <c r="G18" t="inlineStr">
         <is>
@@ -1024,16 +1024,16 @@
         <v>18</v>
       </c>
       <c r="C19" t="n">
-        <v>36.89624060182388</v>
+        <v>5.995639097796381</v>
       </c>
       <c r="D19" t="n">
-        <v>2.495726209871906</v>
+        <v>0.4055555091041848</v>
       </c>
       <c r="E19" t="n">
-        <v>12.78042031339302</v>
+        <v>2.076818300926367</v>
       </c>
       <c r="F19" t="n">
-        <v>11.58792849519896</v>
+        <v>1.883038380469831</v>
       </c>
       <c r="G19" t="inlineStr">
         <is>
@@ -1056,16 +1056,16 @@
         <v>19</v>
       </c>
       <c r="C20" t="n">
-        <v>9.57327070573141</v>
+        <v>1.555656489681354</v>
       </c>
       <c r="D20" t="n">
-        <v>17.60536152132051</v>
+        <v>2.860871247214583</v>
       </c>
       <c r="E20" t="n">
-        <v>12.78042031339302</v>
+        <v>2.076818300926367</v>
       </c>
       <c r="F20" t="n">
-        <v>11.58792849519896</v>
+        <v>1.883038380469831</v>
       </c>
       <c r="G20" t="inlineStr">
         <is>
@@ -1088,16 +1088,16 @@
         <v>20</v>
       </c>
       <c r="C21" t="n">
-        <v>44.69257531650493</v>
+        <v>7.262543488932051</v>
       </c>
       <c r="D21" t="n">
-        <v>17.5143294507986</v>
+        <v>2.846078535754772</v>
       </c>
       <c r="E21" t="n">
-        <v>12.78042031339302</v>
+        <v>2.076818300926367</v>
       </c>
       <c r="F21" t="n">
-        <v>11.58792849519896</v>
+        <v>1.883038380469831</v>
       </c>
       <c r="G21" t="inlineStr">
         <is>
@@ -1120,16 +1120,16 @@
         <v>21</v>
       </c>
       <c r="C22" t="n">
-        <v>45.45868645816847</v>
+        <v>7.387036549452377</v>
       </c>
       <c r="D22" t="n">
-        <v>26.85816656272559</v>
+        <v>4.364452066442909</v>
       </c>
       <c r="E22" t="n">
-        <v>12.78042031339302</v>
+        <v>2.076818300926367</v>
       </c>
       <c r="F22" t="n">
-        <v>11.58792849519896</v>
+        <v>1.883038380469831</v>
       </c>
       <c r="G22" t="inlineStr">
         <is>
@@ -1152,16 +1152,16 @@
         <v>22</v>
       </c>
       <c r="C23" t="n">
-        <v>35.84914678644326</v>
+        <v>5.82548635279703</v>
       </c>
       <c r="D23" t="n">
-        <v>42.71254044318965</v>
+        <v>6.940787822018318</v>
       </c>
       <c r="E23" t="n">
-        <v>12.78042031339302</v>
+        <v>2.076818300926367</v>
       </c>
       <c r="F23" t="n">
-        <v>11.58792849519896</v>
+        <v>1.883038380469831</v>
       </c>
       <c r="G23" t="inlineStr">
         <is>
@@ -1184,16 +1184,16 @@
         <v>23</v>
       </c>
       <c r="C24" t="n">
-        <v>13.35010519216891</v>
+        <v>2.169392093727448</v>
       </c>
       <c r="D24" t="n">
-        <v>14.86260670154073</v>
+        <v>2.415173589000368</v>
       </c>
       <c r="E24" t="n">
-        <v>12.78042031339302</v>
+        <v>2.076818300926367</v>
       </c>
       <c r="F24" t="n">
-        <v>11.58792849519896</v>
+        <v>1.883038380469831</v>
       </c>
       <c r="G24" t="inlineStr">
         <is>
@@ -1216,16 +1216,16 @@
         <v>24</v>
       </c>
       <c r="C25" t="n">
-        <v>45.9891170985637</v>
+        <v>7.473231528516602</v>
       </c>
       <c r="D25" t="n">
-        <v>40.89145523347281</v>
+        <v>6.644861475439332</v>
       </c>
       <c r="E25" t="n">
-        <v>12.78042031339302</v>
+        <v>2.076818300926367</v>
       </c>
       <c r="F25" t="n">
-        <v>11.58792849519896</v>
+        <v>1.883038380469831</v>
       </c>
       <c r="G25" t="inlineStr">
         <is>
@@ -1248,16 +1248,16 @@
         <v>25</v>
       </c>
       <c r="C26" t="n">
-        <v>9.509155392629728</v>
+        <v>1.545237751302331</v>
       </c>
       <c r="D26" t="n">
-        <v>15.09026298843196</v>
+        <v>2.452167735620194</v>
       </c>
       <c r="E26" t="n">
-        <v>12.78042031339302</v>
+        <v>2.076818300926367</v>
       </c>
       <c r="F26" t="n">
-        <v>11.58792849519896</v>
+        <v>1.883038380469831</v>
       </c>
       <c r="G26" t="inlineStr">
         <is>
@@ -1280,16 +1280,16 @@
         <v>26</v>
       </c>
       <c r="C27" t="n">
-        <v>13.08316378574737</v>
+        <v>2.126014115183947</v>
       </c>
       <c r="D27" t="n">
-        <v>15.04460856600259</v>
+        <v>2.44474889197542</v>
       </c>
       <c r="E27" t="n">
-        <v>12.78042031339302</v>
+        <v>2.076818300926367</v>
       </c>
       <c r="F27" t="n">
-        <v>11.58792849519896</v>
+        <v>1.883038380469831</v>
       </c>
       <c r="G27" t="inlineStr">
         <is>
@@ -1312,16 +1312,16 @@
         <v>27</v>
       </c>
       <c r="C28" t="n">
-        <v>3.071338712093398</v>
+        <v>0.4990925407151773</v>
       </c>
       <c r="D28" t="n">
-        <v>0.8977744822233376</v>
+        <v>0.1458883533612924</v>
       </c>
       <c r="E28" t="n">
-        <v>12.78042031339302</v>
+        <v>2.076818300926367</v>
       </c>
       <c r="F28" t="n">
-        <v>11.58792849519896</v>
+        <v>1.883038380469831</v>
       </c>
       <c r="G28" t="inlineStr">
         <is>
@@ -1344,16 +1344,16 @@
         <v>28</v>
       </c>
       <c r="C29" t="n">
-        <v>6.617361844253177</v>
+        <v>1.075321299691141</v>
       </c>
       <c r="D29" t="n">
-        <v>16.16569148431917</v>
+        <v>2.626924866201866</v>
       </c>
       <c r="E29" t="n">
-        <v>12.78042031339302</v>
+        <v>2.076818300926367</v>
       </c>
       <c r="F29" t="n">
-        <v>11.58792849519896</v>
+        <v>1.883038380469831</v>
       </c>
       <c r="G29" t="inlineStr">
         <is>
